--- a/templates/west_northants_sized_unitary/model_snapshot_scenario_template_west_northants_sized.xlsx
+++ b/templates/west_northants_sized_unitary/model_snapshot_scenario_template_west_northants_sized.xlsx
@@ -1074,10 +1074,10 @@
         <v>scn-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Base Case 2026/27</v>
+        <v>Base Case 2026/27 (Near Balanced ~£2m gap)</v>
       </c>
       <c r="C2" t="str">
-        <v>Planning baseline aligned to approved budget assumptions</v>
+        <v>Near-balanced planning baseline over 5 years with a very small residual structural gap.</v>
       </c>
       <c r="D2" t="str">
         <v>base</v>
@@ -1092,34 +1092,34 @@
         <v>4.95</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="L2">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M2">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="P2">
-        <v>30000</v>
+        <v>309000</v>
       </c>
       <c r="Q2">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="R2" t="str">
         <v>true</v>
@@ -1128,13 +1128,13 @@
         <v>false</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -1476,7 +1476,7 @@
         <v>businessRatesGrowth</v>
       </c>
       <c r="C3">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D3" t="str">
         <v>%</v>
@@ -1490,7 +1490,7 @@
         <v>grantVariation</v>
       </c>
       <c r="C4">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="str">
         <v>%</v>
@@ -1504,7 +1504,7 @@
         <v>feesChargesElasticity</v>
       </c>
       <c r="C5">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D5" t="str">
         <v>%</v>
@@ -1518,7 +1518,7 @@
         <v>payAward</v>
       </c>
       <c r="C6">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="D6" t="str">
         <v>%</v>
@@ -1532,7 +1532,7 @@
         <v>nonPayInflation</v>
       </c>
       <c r="C7">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="str">
         <v>%</v>
@@ -1546,7 +1546,7 @@
         <v>ascDemandGrowth</v>
       </c>
       <c r="C8">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D8" t="str">
         <v>%</v>
@@ -1560,7 +1560,7 @@
         <v>cscDemandGrowth</v>
       </c>
       <c r="C9">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="D9" t="str">
         <v>%</v>
@@ -1574,7 +1574,7 @@
         <v>savingsDeliveryRisk</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D10" t="str">
         <v>%</v>
@@ -1588,7 +1588,7 @@
         <v>annualSavingsTarget</v>
       </c>
       <c r="C11">
-        <v>30000</v>
+        <v>309000</v>
       </c>
       <c r="D11" t="str">
         <v>£000</v>
@@ -1602,7 +1602,7 @@
         <v>reservesUsage</v>
       </c>
       <c r="C12">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="D12" t="str">
         <v>£000</v>
@@ -1644,7 +1644,7 @@
         <v>inflationRate</v>
       </c>
       <c r="C15">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="D15" t="str">
         <v>%</v>
@@ -2396,7 +2396,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2727,9 +2727,56 @@
         <v>100</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>sav-900</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Strategic Transformation Programme (corporate)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Corporate-wide recurring savings envelope to support a near-balanced medium-term financial strategy.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>transformation</v>
+      </c>
+      <c r="E8">
+        <v>309000</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>95</v>
+      </c>
+      <c r="H8" t="str">
+        <v>true</v>
+      </c>
+      <c r="I8" t="str">
+        <v>amber</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Corporate Leadership Team</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
   </ignoredErrors>
 </worksheet>
 </file>
